--- a/dataset_t6_grouped/results2/G4/G4_T1936_W0015F0002T0006Z000C1N16_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T1936_W0015F0002T0006Z000C1N16_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>12.85149895624937</v>
+        <v>2.088368580390523</v>
       </c>
       <c r="D2" t="n">
-        <v>12.53553928925394</v>
+        <v>2.037025134503765</v>
       </c>
       <c r="E2" t="n">
-        <v>9.260656933875866</v>
+        <v>1.504856751754828</v>
       </c>
       <c r="F2" t="n">
-        <v>3.269179074500656</v>
+        <v>0.5312415996063566</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>24.23250800789006</v>
+        <v>3.937782551282135</v>
       </c>
       <c r="D3" t="n">
-        <v>5.12694517997955</v>
+        <v>0.8331285917466769</v>
       </c>
       <c r="E3" t="n">
-        <v>9.260656933875866</v>
+        <v>1.504856751754828</v>
       </c>
       <c r="F3" t="n">
-        <v>3.269179074500656</v>
+        <v>0.5312415996063566</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>11.88577218260682</v>
+        <v>1.931437979673608</v>
       </c>
       <c r="D4" t="n">
-        <v>10.47865139236968</v>
+        <v>1.702780851260073</v>
       </c>
       <c r="E4" t="n">
-        <v>9.260656933875866</v>
+        <v>1.504856751754828</v>
       </c>
       <c r="F4" t="n">
-        <v>3.269179074500656</v>
+        <v>0.5312415996063566</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>26.64828033222776</v>
+        <v>4.33034555398701</v>
       </c>
       <c r="D5" t="n">
-        <v>10.09189642519136</v>
+        <v>1.639933169093596</v>
       </c>
       <c r="E5" t="n">
-        <v>9.260656933875866</v>
+        <v>1.504856751754828</v>
       </c>
       <c r="F5" t="n">
-        <v>3.269179074500656</v>
+        <v>0.5312415996063566</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>14.95483164614983</v>
+        <v>2.430160142499348</v>
       </c>
       <c r="D6" t="n">
-        <v>15.35112118777834</v>
+        <v>2.49455719301398</v>
       </c>
       <c r="E6" t="n">
-        <v>9.260656933875866</v>
+        <v>1.504856751754828</v>
       </c>
       <c r="F6" t="n">
-        <v>3.269179074500656</v>
+        <v>0.5312415996063566</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>6.223417099152728</v>
+        <v>1.011305278612318</v>
       </c>
       <c r="D7" t="n">
-        <v>6.084466389558453</v>
+        <v>0.9887257883032486</v>
       </c>
       <c r="E7" t="n">
-        <v>9.260656933875866</v>
+        <v>1.504856751754828</v>
       </c>
       <c r="F7" t="n">
-        <v>3.269179074500656</v>
+        <v>0.5312415996063566</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>34.70801873297422</v>
+        <v>5.640053044108311</v>
       </c>
       <c r="D8" t="n">
-        <v>9.218634074642436</v>
+        <v>1.498028037129396</v>
       </c>
       <c r="E8" t="n">
-        <v>9.260656933875866</v>
+        <v>1.504856751754828</v>
       </c>
       <c r="F8" t="n">
-        <v>3.269179074500656</v>
+        <v>0.5312415996063566</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
